--- a/Download/ZoneCEV/ZCEV.xlsx
+++ b/Download/ZoneCEV/ZCEV.xlsx
@@ -1936,7 +1936,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>

--- a/Download/ZoneCEV/ZCEV.xlsx
+++ b/Download/ZoneCEV/ZCEV.xlsx
@@ -1045,7 +1045,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
